--- a/exports/NTPC_full_report.xlsx
+++ b/exports/NTPC_full_report.xlsx
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -6968,16 +6968,16 @@
         <v>292.05</v>
       </c>
       <c r="E59" t="n">
-        <v>302.5</v>
+        <v>304.5</v>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
         <v>10.05</v>
       </c>
       <c r="H59" t="n">
-        <v>-5.7</v>
+        <v>-5.08</v>
       </c>
       <c r="I59" t="n">
         <v>1.09</v>

--- a/exports/NTPC_full_report.xlsx
+++ b/exports/NTPC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44599.55208333334</v>
+        <v>44600.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>135.15</v>
+        <v>133.75</v>
       </c>
       <c r="I2" t="n">
         <v>133.9343212450051</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="L2" t="n">
         <v>0.3</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.58</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>133.05</v>
+        <v>133.55</v>
       </c>
       <c r="I3" t="n">
         <v>133.313260843501</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="L3" t="n">
         <v>2.95</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.95</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44691.55208333334</v>
+        <v>44692.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>155.1</v>
+        <v>150.6</v>
       </c>
       <c r="I4" t="n">
         <v>154.8236444719334</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>71</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>16.14</v>
+        <v>12.77</v>
       </c>
       <c r="L4" t="n">
         <v>4.98</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>154.2</v>
+        <v>157.7</v>
       </c>
       <c r="I5" t="n">
         <v>157.3010072552269</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.39</v>
+        <v>-4.71</v>
       </c>
       <c r="L5" t="n">
-        <v>4.22</v>
+        <v>4.91</v>
       </c>
       <c r="M5" t="n">
         <v>3.38</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.44</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.38541666666</v>
+        <v>44727.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>148.9</v>
+        <v>148.25</v>
       </c>
       <c r="I6" t="n">
         <v>148.6882137627626</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.58</v>
+        <v>-5.99</v>
       </c>
       <c r="L6" t="n">
-        <v>6.31</v>
+        <v>6.44</v>
       </c>
       <c r="M6" t="n">
         <v>0.99</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.22</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44753.55208333334</v>
+        <v>44754.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>144.8</v>
+        <v>147.15</v>
       </c>
       <c r="I7" t="n">
         <v>145.0135127163499</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>2.33</v>
+        <v>0.74</v>
       </c>
       <c r="L7" t="n">
         <v>1.25</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.62</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>169.05</v>
+        <v>166</v>
       </c>
       <c r="I8" t="n">
         <v>167.27902710815</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K8" t="n">
-        <v>14.88</v>
+        <v>12.81</v>
       </c>
       <c r="L8" t="n">
         <v>2.11</v>
@@ -897,7 +992,7 @@
         <v>1.88</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.42</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.01</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44847.55208333334</v>
+        <v>44848.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>165</v>
+        <v>166.25</v>
       </c>
       <c r="I9" t="n">
         <v>166.1247829143192</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6</v>
+        <v>-0.15</v>
       </c>
       <c r="L9" t="n">
         <v>1.48</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.07</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>173.25</v>
+        <v>171</v>
       </c>
       <c r="I10" t="n">
         <v>171.4914703075522</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>4.21</v>
+        <v>2.86</v>
       </c>
       <c r="L10" t="n">
         <v>2.86</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.05</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>171.05</v>
+        <v>172.3</v>
       </c>
       <c r="I11" t="n">
         <v>171.0594590316593</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03</v>
+        <v>-0.76</v>
       </c>
       <c r="L11" t="n">
         <v>1.84</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>3.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>171.1</v>
+        <v>169.2</v>
       </c>
       <c r="I12" t="n">
         <v>169.5507262189975</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7</v>
+        <v>-1.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>2.23</v>
       </c>
       <c r="M12" t="n">
         <v>0.51</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.14</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44932.55208333334</v>
+        <v>44935.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>169.25</v>
+        <v>170.5</v>
       </c>
       <c r="I13" t="n">
         <v>170.3364322673416</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.03</v>
+        <v>-0.77</v>
       </c>
       <c r="L13" t="n">
         <v>2.87</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>3.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>167.45</v>
+        <v>164.25</v>
       </c>
       <c r="I14" t="n">
         <v>164.7502565917373</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.79</v>
+        <v>-3.67</v>
       </c>
       <c r="L14" t="n">
-        <v>3.81</v>
+        <v>4.63</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06</v>
+        <v>1.76</v>
       </c>
       <c r="N14" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
         <v>0.59</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.17</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44977.55208333334</v>
+        <v>44978.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>168</v>
+        <v>173.25</v>
       </c>
       <c r="I15" t="n">
         <v>170.6943525798851</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.28</v>
+        <v>-5.48</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>6.09</v>
       </c>
       <c r="M15" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.98</v>
       </c>
       <c r="O15" t="n">
         <v>-1.52</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.01</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45009.38541666666</v>
+        <v>45009.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>174.25</v>
+        <v>172.75</v>
       </c>
       <c r="I16" t="n">
         <v>173.6279772239672</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="L16" t="n">
         <v>2.74</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.94</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>177.45</v>
+        <v>177.9</v>
       </c>
       <c r="I17" t="n">
         <v>177.6616461243112</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.72</v>
+        <v>-2.98</v>
       </c>
       <c r="L17" t="n">
         <v>3.07</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.04</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>173.1</v>
+        <v>169.85</v>
       </c>
       <c r="I18" t="n">
         <v>172.0131820496746</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.7</v>
+        <v>-4.53</v>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>4.86</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06</v>
+        <v>0.43</v>
       </c>
       <c r="N18" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="O18" t="n">
         <v>1.31</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.12</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>172</v>
+        <v>175.15</v>
       </c>
       <c r="I19" t="n">
         <v>173.4226623086475</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.27</v>
+        <v>-3.12</v>
       </c>
       <c r="L19" t="n">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
         <v>0.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
         <v>-1.94</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.22</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>175.15</v>
+        <v>173.15</v>
       </c>
       <c r="I20" t="n">
         <v>173.9250456519144</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.08</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45084.55208333334</v>
+        <v>45085.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>177.9</v>
+        <v>181.9</v>
       </c>
       <c r="I21" t="n">
         <v>179.2294219686189</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.74</v>
+        <v>-5.05</v>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>6.38</v>
       </c>
       <c r="M21" t="n">
         <v>0.92</v>
       </c>
       <c r="N21" t="n">
-        <v>1.37</v>
+        <v>2.78</v>
       </c>
       <c r="O21" t="n">
         <v>-1.06</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45119.55208333334</v>
+        <v>45120.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>190.75</v>
+        <v>188.25</v>
       </c>
       <c r="I22" t="n">
         <v>188.605755159188</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.87</v>
+        <v>3.49</v>
       </c>
       <c r="L22" t="n">
         <v>2.09</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.01</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45127.55208333334</v>
+        <v>45128.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>192.8</v>
+        <v>196.05</v>
       </c>
       <c r="I23" t="n">
         <v>194.0211105839304</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.42</v>
+        <v>-4.14</v>
       </c>
       <c r="L23" t="n">
         <v>4.44</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.35</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45152.38541666666</v>
+        <v>45152.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>213.35</v>
+        <v>213.05</v>
       </c>
       <c r="I24" t="n">
         <v>213.0820494787033</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="L24" t="n">
         <v>2.01</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>221.25</v>
+        <v>221.85</v>
       </c>
       <c r="I25" t="n">
         <v>221.8054982948931</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.85</v>
+        <v>-4.13</v>
       </c>
       <c r="L25" t="n">
-        <v>4.34</v>
+        <v>4.62</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45203.55208333334</v>
+        <v>45204.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>235.45</v>
+        <v>233.75</v>
       </c>
       <c r="I26" t="n">
         <v>234.6236525195765</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>6.13</v>
+        <v>5.36</v>
       </c>
       <c r="L26" t="n">
         <v>2.57</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.07</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>243.1</v>
+        <v>246.65</v>
       </c>
       <c r="I27" t="n">
         <v>244.9247248297246</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>-4</v>
+        <v>-5.52</v>
       </c>
       <c r="L27" t="n">
-        <v>4.81</v>
+        <v>5.75</v>
       </c>
       <c r="M27" t="n">
         <v>0.76</v>
       </c>
       <c r="N27" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="O27" t="n">
         <v>-0.49</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.64</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>241.15</v>
+        <v>236.45</v>
       </c>
       <c r="I28" t="n">
         <v>236.7607611531682</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.23</v>
+        <v>-4.14</v>
       </c>
       <c r="L28" t="n">
-        <v>3.69</v>
+        <v>4.28</v>
       </c>
       <c r="M28" t="n">
         <v>0.89</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
         <v>1.11</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>4.99</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45240.38541666666</v>
+        <v>45240.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>240.75</v>
+        <v>242.5</v>
       </c>
       <c r="I29" t="n">
         <v>241.8927032280922</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.82</v>
+        <v>-2.56</v>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="M29" t="n">
         <v>0.73</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.88</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>309.6</v>
+        <v>299.45</v>
       </c>
       <c r="I30" t="n">
         <v>304.8579034358621</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>68</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>27.67</v>
+        <v>23.48</v>
       </c>
       <c r="L30" t="n">
         <v>0.78</v>
@@ -2151,7 +2510,7 @@
         <v>1.92</v>
       </c>
       <c r="N30" t="n">
-        <v>2.57</v>
+        <v>3.23</v>
       </c>
       <c r="O30" t="n">
         <v>2.02</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45315.55208333334</v>
+        <v>45316.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>308</v>
+        <v>315.5</v>
       </c>
       <c r="I31" t="n">
         <v>315.0443779981607</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.86</v>
+        <v>-5.36</v>
       </c>
       <c r="L31" t="n">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="M31" t="n">
         <v>1.44</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>317</v>
+        <v>316.1</v>
       </c>
       <c r="I32" t="n">
         <v>316.4238851431783</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.06</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45337.38541666666</v>
+        <v>45337.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>337.15</v>
+        <v>340.9</v>
       </c>
       <c r="I33" t="n">
         <v>338.421639255305</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.66</v>
+        <v>-7.85</v>
       </c>
       <c r="L33" t="n">
-        <v>6.8</v>
+        <v>7.85</v>
       </c>
       <c r="M33" t="n">
         <v>0.78</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.61</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>344.2</v>
+        <v>327.9</v>
       </c>
       <c r="I34" t="n">
         <v>341.9102412320537</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>0.97</v>
+        <v>-3.81</v>
       </c>
       <c r="L34" t="n">
-        <v>3.02</v>
+        <v>5.15</v>
       </c>
       <c r="M34" t="n">
         <v>0.41</v>
       </c>
       <c r="N34" t="n">
-        <v>2.92</v>
+        <v>6.55</v>
       </c>
       <c r="O34" t="n">
         <v>3.79</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>329.8</v>
+        <v>337.2</v>
       </c>
       <c r="I35" t="n">
         <v>334.6821022999195</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.58</v>
+        <v>-2.84</v>
       </c>
       <c r="L35" t="n">
         <v>5.06</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>6.67</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>353.4</v>
+        <v>348.7</v>
       </c>
       <c r="I36" t="n">
         <v>348.891158202818</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>4.8</v>
+        <v>3.41</v>
       </c>
       <c r="L36" t="n">
         <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>1.75</v>
+        <v>2.91</v>
       </c>
       <c r="N36" t="n">
         <v>1.61</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.62</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45412.55208333334</v>
+        <v>45414.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>363</v>
+        <v>370.5</v>
       </c>
       <c r="I37" t="n">
         <v>363.9001580282859</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.1</v>
+        <v>-6.25</v>
       </c>
       <c r="L37" t="n">
-        <v>4.8</v>
+        <v>6.31</v>
       </c>
       <c r="M37" t="n">
         <v>1.57</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.25</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>356.45</v>
+        <v>347.4</v>
       </c>
       <c r="I38" t="n">
         <v>354.6046287480125</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.79</v>
+        <v>-6.23</v>
       </c>
       <c r="L38" t="n">
-        <v>4.35</v>
+        <v>6.28</v>
       </c>
       <c r="M38" t="n">
         <v>0.03</v>
       </c>
       <c r="N38" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
         <v>1.63</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.82</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>366</v>
+        <v>372.45</v>
       </c>
       <c r="I39" t="n">
         <v>369.3814894543934</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.35</v>
+        <v>-7.21</v>
       </c>
       <c r="L39" t="n">
-        <v>5.93</v>
+        <v>7.69</v>
       </c>
       <c r="M39" t="n">
         <v>0.75</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.82</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>361</v>
+        <v>357.8</v>
       </c>
       <c r="I40" t="n">
         <v>358.6599938008178</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.07</v>
+        <v>-3.93</v>
       </c>
       <c r="L40" t="n">
-        <v>4.11</v>
+        <v>4.55</v>
       </c>
       <c r="M40" t="n">
         <v>0.82</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6.07</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>359.65</v>
+        <v>390.6</v>
       </c>
       <c r="I41" t="n">
         <v>377.8009942194077</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.52</v>
+        <v>-9.17</v>
       </c>
       <c r="L41" t="n">
-        <v>2.47</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0.68</v>
+        <v>7.05</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>9.27</v>
       </c>
       <c r="O41" t="n">
         <v>-0.37</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.69</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>393</v>
+        <v>339.05</v>
       </c>
       <c r="I42" t="n">
         <v>365.7381946822798</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.61</v>
+        <v>-13.2</v>
       </c>
       <c r="L42" t="n">
-        <v>4.39</v>
+        <v>19.62</v>
       </c>
       <c r="M42" t="n">
-        <v>-0</v>
+        <v>0.28</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>14.78</v>
       </c>
       <c r="O42" t="n">
         <v>9.27</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>17.69</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45470.55208333334</v>
+        <v>45471.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>376.6</v>
+        <v>382.6</v>
       </c>
       <c r="I43" t="n">
         <v>378.0032704253072</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.08</v>
+        <v>-12.84</v>
       </c>
       <c r="L43" t="n">
         <v>15.59</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.45</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>370.4</v>
+        <v>364.9</v>
       </c>
       <c r="I44" t="n">
         <v>368.0956120550849</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.19</v>
+        <v>-4.63</v>
       </c>
       <c r="L44" t="n">
-        <v>4.56</v>
+        <v>5.15</v>
       </c>
       <c r="M44" t="n">
         <v>0.07000000000000001</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.04</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45497.38541666666</v>
+        <v>45497.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>386.75</v>
+        <v>392.65</v>
       </c>
       <c r="I45" t="n">
         <v>386.9463078088336</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.99</v>
+        <v>-7.6</v>
       </c>
       <c r="L45" t="n">
-        <v>7.78</v>
+        <v>8.25</v>
       </c>
       <c r="M45" t="n">
         <v>1.06</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.3</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45516.55208333334</v>
+        <v>45517.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>401.8</v>
+        <v>398.7</v>
       </c>
       <c r="I46" t="n">
         <v>399.334486863977</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="L46" t="n">
         <v>1.63</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>6.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45534.38541666666</v>
+        <v>45534.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>414.6</v>
+        <v>417.2</v>
       </c>
       <c r="I47" t="n">
         <v>416.7359279185462</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.99</v>
+        <v>-4.64</v>
       </c>
       <c r="L47" t="n">
-        <v>4.39</v>
+        <v>5.14</v>
       </c>
       <c r="M47" t="n">
         <v>0.78</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>4.22</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>403</v>
+        <v>396.55</v>
       </c>
       <c r="I48" t="n">
         <v>399.5887984069686</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.4</v>
+        <v>-4.95</v>
       </c>
       <c r="L48" t="n">
-        <v>4.15</v>
+        <v>5.87</v>
       </c>
       <c r="M48" t="n">
         <v>1.83</v>
       </c>
       <c r="N48" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
         <v>1.45</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.21</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>401.45</v>
+        <v>408.9</v>
       </c>
       <c r="I49" t="n">
         <v>407.202104159105</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.24</v>
+        <v>-3.11</v>
       </c>
       <c r="L49" t="n">
-        <v>2.71</v>
+        <v>3.33</v>
       </c>
       <c r="M49" t="n">
         <v>0.52</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.74</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>431.15</v>
+        <v>413.65</v>
       </c>
       <c r="I50" t="n">
         <v>422.592248427298</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>5.44</v>
+        <v>1.16</v>
       </c>
       <c r="L50" t="n">
         <v>1.69</v>
@@ -3291,7 +3890,7 @@
         <v>2.03</v>
       </c>
       <c r="N50" t="n">
-        <v>1.27</v>
+        <v>3.26</v>
       </c>
       <c r="O50" t="n">
         <v>2.53</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>312.3</v>
+        <v>321.15</v>
       </c>
       <c r="I51" t="n">
         <v>320.1590106157678</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>99.16666666666667</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
-        <v>24.5</v>
+        <v>22.36</v>
       </c>
       <c r="L51" t="n">
         <v>4.68</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>7.69</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>318</v>
+        <v>307.55</v>
       </c>
       <c r="I52" t="n">
         <v>316.7883359146622</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.98</v>
+        <v>-4.23</v>
       </c>
       <c r="L52" t="n">
-        <v>4.05</v>
+        <v>5.34</v>
       </c>
       <c r="M52" t="n">
-        <v>0.54</v>
+        <v>2.48</v>
       </c>
       <c r="N52" t="n">
         <v>3.12</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.73</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>314.1</v>
+        <v>324.65</v>
       </c>
       <c r="I53" t="n">
         <v>315.5604754979473</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.13</v>
+        <v>-5.56</v>
       </c>
       <c r="L53" t="n">
-        <v>5.04</v>
+        <v>6.05</v>
       </c>
       <c r="M53" t="n">
         <v>0.91</v>
       </c>
       <c r="N53" t="n">
-        <v>3.24</v>
+        <v>3.49</v>
       </c>
       <c r="O53" t="n">
         <v>-1.89</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.84</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>315.7</v>
+        <v>307.85</v>
       </c>
       <c r="I54" t="n">
         <v>308.3746805289628</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.76</v>
+        <v>-5.17</v>
       </c>
       <c r="L54" t="n">
-        <v>4.05</v>
+        <v>5.58</v>
       </c>
       <c r="M54" t="n">
         <v>0.92</v>
       </c>
       <c r="N54" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="O54" t="n">
         <v>3.49</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>6.22</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>325.8</v>
+        <v>332.95</v>
       </c>
       <c r="I55" t="n">
         <v>326.9561399814504</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.83</v>
+        <v>-8.15</v>
       </c>
       <c r="L55" t="n">
-        <v>6.32</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.37</v>
+        <v>0.98</v>
       </c>
       <c r="N55" t="n">
         <v>3.91</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>7.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>350.65</v>
+        <v>345.25</v>
       </c>
       <c r="I56" t="n">
         <v>349.8508907331991</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>5.32</v>
+        <v>3.69</v>
       </c>
       <c r="L56" t="n">
         <v>2.93</v>
       </c>
       <c r="M56" t="n">
-        <v>1.58</v>
+        <v>6.46</v>
       </c>
       <c r="N56" t="n">
         <v>3.04</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>4.4</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>359.5</v>
+        <v>367.25</v>
       </c>
       <c r="I57" t="n">
         <v>360.4310284192146</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.13</v>
+        <v>-6.37</v>
       </c>
       <c r="L57" t="n">
-        <v>4.71</v>
+        <v>6.72</v>
       </c>
       <c r="M57" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="N57" t="n">
         <v>2.44</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>348.5</v>
+        <v>341.3</v>
       </c>
       <c r="I58" t="n">
         <v>347.5575966213372</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.11</v>
+        <v>-7.07</v>
       </c>
       <c r="L58" t="n">
-        <v>5.91</v>
+        <v>7.39</v>
       </c>
       <c r="M58" t="n">
         <v>0.51</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.17</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45817.55208333334</v>
+        <v>45818.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>337</v>
+        <v>339.9</v>
       </c>
       <c r="I59" t="n">
         <v>339.4131085668311</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K59" t="n">
-        <v>1.26</v>
+        <v>0.41</v>
       </c>
       <c r="L59" t="n">
         <v>2.9</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>3.42</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>333.6</v>
+        <v>330.35</v>
       </c>
       <c r="I60" t="n">
         <v>331.0865485612654</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.85</v>
+        <v>-2.81</v>
       </c>
       <c r="L60" t="n">
-        <v>2.13</v>
+        <v>3.91</v>
       </c>
       <c r="M60" t="n">
-        <v>0.03</v>
+        <v>2.04</v>
       </c>
       <c r="N60" t="n">
         <v>1.35</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>3.45</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45845.55208333334</v>
+        <v>45846.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>338.15</v>
+        <v>340.55</v>
       </c>
       <c r="I61" t="n">
         <v>340.3792502562299</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.36</v>
+        <v>-3.09</v>
       </c>
       <c r="L61" t="n">
-        <v>3.31</v>
+        <v>3.68</v>
       </c>
       <c r="M61" t="n">
         <v>0.5600000000000001</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>3.61</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>338.9</v>
+        <v>335.3</v>
       </c>
       <c r="I62" t="n">
         <v>335.3793065056516</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.48</v>
+        <v>-1.54</v>
       </c>
       <c r="L62" t="n">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
       <c r="M62" t="n">
         <v>0.25</v>
       </c>
       <c r="N62" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="O62" t="n">
         <v>1.43</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>3.35</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>336.05</v>
+        <v>341.6</v>
       </c>
       <c r="I63" t="n">
         <v>339.9115694182876</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.22</v>
+        <v>-1.88</v>
       </c>
       <c r="L63" t="n">
         <v>2.09</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.55</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>331.9</v>
+        <v>330.9</v>
       </c>
       <c r="I64" t="n">
         <v>330.9892854863267</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.84</v>
+        <v>-3.13</v>
       </c>
       <c r="L64" t="n">
         <v>3.78</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.35</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45916.38541666666</v>
+        <v>45916.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>334.2</v>
+        <v>335</v>
       </c>
       <c r="I65" t="n">
         <v>334.7125747582638</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>-1</v>
+        <v>-1.24</v>
       </c>
       <c r="L65" t="n">
         <v>2.22</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>3.01</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45937.55208333334</v>
+        <v>45938.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>338.25</v>
+        <v>334.05</v>
       </c>
       <c r="I66" t="n">
         <v>337.408236670513</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>0.97</v>
+        <v>-0.28</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M66" t="n">
         <v>0.55</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>3.97</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>338.95</v>
+        <v>349.6</v>
       </c>
       <c r="I67" t="n">
         <v>344.9201669272559</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.47</v>
+        <v>-4.65</v>
       </c>
       <c r="L67" t="n">
-        <v>3.34</v>
+        <v>4.77</v>
       </c>
       <c r="M67" t="n">
         <v>0.53</v>
       </c>
       <c r="N67" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.97</v>
       </c>
       <c r="O67" t="n">
         <v>-1.26</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.84</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>336.65</v>
+        <v>335.6</v>
       </c>
       <c r="I68" t="n">
         <v>336.3315196939989</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.7</v>
+        <v>-4</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="M68" t="n">
         <v>0.07000000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>3.63</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>325.25</v>
+        <v>330</v>
       </c>
       <c r="I69" t="n">
         <v>326.5268648015407</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K69" t="n">
-        <v>3.08</v>
+        <v>1.67</v>
       </c>
       <c r="L69" t="n">
         <v>0.57</v>
@@ -4374,7 +5201,7 @@
         <v>0.58</v>
       </c>
       <c r="N69" t="n">
-        <v>0.96</v>
+        <v>1.43</v>
       </c>
       <c r="O69" t="n">
         <v>-0.37</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>3.28</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>342.5</v>
+        <v>337.15</v>
       </c>
       <c r="I70" t="n">
         <v>338.7716447873117</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K70" t="n">
-        <v>3.79</v>
+        <v>2.17</v>
       </c>
       <c r="L70" t="n">
         <v>1.61</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>5.17</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>337.7</v>
+        <v>349.85</v>
       </c>
       <c r="I71" t="n">
         <v>349.7785541248654</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.16</v>
+        <v>-3.77</v>
       </c>
       <c r="L71" t="n">
-        <v>2.15</v>
+        <v>3.96</v>
       </c>
       <c r="M71" t="n">
         <v>0.55</v>
       </c>
       <c r="N71" t="n">
-        <v>0.34</v>
+        <v>3.35</v>
       </c>
       <c r="O71" t="n">
         <v>-1.8</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.24</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>377</v>
+        <v>366.95</v>
       </c>
       <c r="I72" t="n">
         <v>370.2248598933753</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K72" t="n">
-        <v>7.76</v>
+        <v>4.89</v>
       </c>
       <c r="L72" t="n">
         <v>3.93</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>6.37</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46092.55208333334</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>378.75</v>
+        <v>387.45</v>
       </c>
       <c r="I73" t="n">
         <v>386.6980918250578</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.22</v>
+        <v>-5.59</v>
       </c>
       <c r="L73" t="n">
-        <v>5.07</v>
+        <v>5.93</v>
       </c>
       <c r="M73" t="n">
         <v>2.43</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>7.21</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>370.45</v>
+        <v>367.6</v>
       </c>
       <c r="I74" t="n">
         <v>368.050022985688</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.39</v>
+        <v>-5.12</v>
       </c>
       <c r="L74" t="n">
-        <v>4.68</v>
+        <v>5.76</v>
       </c>
       <c r="M74" t="n">
         <v>1.65</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>7.07</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46120.55208333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>373</v>
+        <v>381.95</v>
       </c>
       <c r="I75" t="n">
         <v>378.1582577029239</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.47</v>
+        <v>-3.9</v>
       </c>
       <c r="L75" t="n">
-        <v>3.89</v>
+        <v>4.52</v>
       </c>
       <c r="M75" t="n">
         <v>2.93</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>5.97</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>393.55</v>
+        <v>391.6</v>
       </c>
       <c r="I76" t="n">
         <v>392.1026322258994</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K76" t="n">
-        <v>3.04</v>
+        <v>2.53</v>
       </c>
       <c r="L76" t="n">
         <v>2.59</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>4.64</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46191.55208333334</v>
+        <v>46192.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>362</v>
+        <v>365.75</v>
       </c>
       <c r="I77" t="n">
         <v>364.0170931498334</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>7.56</v>
+        <v>6.6</v>
       </c>
       <c r="L77" t="n">
         <v>2.94</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>4.86</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46198.38541666666</v>
+        <v>46198.55208333334</v>
       </c>
       <c r="H78" t="n">
-        <v>354.1</v>
+        <v>352.5</v>
       </c>
       <c r="I78" t="n">
         <v>352.6886683175072</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K78" t="n">
-        <v>-3.19</v>
+        <v>-3.62</v>
       </c>
       <c r="L78" t="n">
-        <v>3.29</v>
+        <v>3.91</v>
       </c>
       <c r="M78" t="n">
         <v>0.19</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>171</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7049,7 +8004,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="6">
@@ -7059,7 +8014,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +8024,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +8034,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +8044,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +8054,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="11">
@@ -7109,7 +8064,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -7119,7 +8074,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -7129,7 +8084,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84.40000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="14">
@@ -7139,7 +8094,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.29</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="15">
@@ -7149,7 +8104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="16">
@@ -7159,7 +8114,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.26</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="17">
@@ -7169,7 +8124,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.67</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="18">
@@ -7179,7 +8134,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35.1</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="19">
@@ -7189,7 +8144,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="20">
@@ -7199,7 +8154,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.15</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="21">
@@ -7209,7 +8164,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.59</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="22">
@@ -7219,7 +8174,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +8184,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -7239,7 +8194,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25">
@@ -7249,7 +8204,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.45</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="26">
@@ -7259,7 +8214,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="27">
@@ -7269,7 +8224,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.57</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="28">
@@ -7279,7 +8234,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
